--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(共通コンポーネント)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(共通コンポーネント)_サンプル.xlsx
@@ -12241,8 +12241,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -12284,8 +12284,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -12321,8 +12321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -12360,8 +12360,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -12395,8 +12395,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -12430,8 +12430,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -12465,8 +12465,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -12500,8 +12500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -12539,8 +12539,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -12574,8 +12574,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -12609,8 +12609,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -12646,8 +12646,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -12681,8 +12681,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -12716,8 +12716,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -12751,8 +12751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -12790,8 +12790,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -12825,8 +12825,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -12864,8 +12864,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -12899,8 +12899,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -12936,8 +12936,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -12971,8 +12971,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -13006,8 +13006,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -13041,8 +13041,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -13078,8 +13078,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -13113,8 +13113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -13150,8 +13150,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -13191,8 +13191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -13226,8 +13226,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -13261,8 +13261,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -13296,8 +13296,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -13335,8 +13335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -13370,8 +13370,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -13413,8 +13413,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -13448,8 +13448,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -13483,8 +13483,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -13520,8 +13520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -13555,8 +13555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -13590,8 +13590,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -13627,8 +13627,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -13662,8 +13662,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -13699,8 +13699,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -13734,8 +13734,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -13769,8 +13769,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -13804,8 +13804,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -13839,8 +13839,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -13874,8 +13874,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -13911,8 +13911,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -13948,8 +13948,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -13985,8 +13985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -14024,8 +14024,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -14059,8 +14059,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -14094,8 +14094,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -14129,8 +14129,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -14164,8 +14164,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -14201,8 +14201,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -14236,8 +14236,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -14271,8 +14271,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -14306,8 +14306,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -14341,8 +14341,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -14376,8 +14376,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -14411,8 +14411,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -14446,8 +14446,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -14483,8 +14483,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -14520,8 +14520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -14555,8 +14555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -14590,8 +14590,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -14625,8 +14625,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -14676,8 +14676,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -14721,8 +14721,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -14758,8 +14758,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -14795,8 +14795,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -14830,8 +14830,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -14867,8 +14867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -14904,8 +14904,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -14945,8 +14945,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -14982,8 +14982,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -15019,8 +15019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -15060,8 +15060,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -15095,8 +15095,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -15132,8 +15132,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -15169,8 +15169,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -15204,8 +15204,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -15241,8 +15241,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -15282,8 +15282,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -15317,8 +15317,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -15352,8 +15352,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -15387,8 +15387,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -15422,8 +15422,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -15459,8 +15459,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -15494,8 +15494,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -15529,8 +15529,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -15564,8 +15564,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -15599,8 +15599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -15636,8 +15636,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -15679,8 +15679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -15720,8 +15720,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -15755,8 +15755,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -15796,8 +15796,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -15837,8 +15837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -15872,8 +15872,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -15915,8 +15915,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -15952,8 +15952,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -15987,8 +15987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -16022,8 +16022,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -16059,8 +16059,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -16094,8 +16094,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -16129,8 +16129,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -16164,8 +16164,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -16199,8 +16199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -16236,8 +16236,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -16271,8 +16271,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -16306,8 +16306,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -16341,8 +16341,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -16376,8 +16376,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -16413,8 +16413,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -16452,8 +16452,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -16493,8 +16493,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -16530,8 +16530,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -16565,8 +16565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -16600,8 +16600,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -16643,8 +16643,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -16680,8 +16680,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -16715,8 +16715,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -16750,8 +16750,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -16787,8 +16787,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -16822,8 +16822,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -16861,8 +16861,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -16902,8 +16902,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -16939,8 +16939,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -16976,8 +16976,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -17013,8 +17013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -17050,8 +17050,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -17087,8 +17087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -17122,8 +17122,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -17157,8 +17157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -17192,8 +17192,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -17227,8 +17227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -17262,8 +17262,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -17301,8 +17301,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -17336,8 +17336,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -17373,8 +17373,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -17408,8 +17408,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -17443,8 +17443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -17478,8 +17478,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -17513,8 +17513,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -17548,8 +17548,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -17583,8 +17583,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -17618,8 +17618,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -17653,8 +17653,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -17688,8 +17688,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -17723,8 +17723,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -17760,8 +17760,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -17795,8 +17795,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -17830,8 +17830,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -17865,8 +17865,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -17900,8 +17900,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -17935,8 +17935,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -17970,8 +17970,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -18007,8 +18007,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -18042,8 +18042,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -18077,8 +18077,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -18112,8 +18112,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -18147,8 +18147,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -18182,8 +18182,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -18217,8 +18217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -18252,8 +18252,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -18287,8 +18287,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -18324,8 +18324,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -18361,8 +18361,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -18404,8 +18404,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -18443,8 +18443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -18482,8 +18482,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -18525,8 +18525,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -18562,8 +18562,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -18597,8 +18597,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -18634,8 +18634,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -18669,8 +18669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -18708,8 +18708,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -18749,8 +18749,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -18784,8 +18784,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -18819,8 +18819,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -18854,8 +18854,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -18889,8 +18889,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -18924,8 +18924,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -18959,8 +18959,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -18996,8 +18996,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -19035,8 +19035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -19070,8 +19070,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -19105,8 +19105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -19140,8 +19140,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -19175,8 +19175,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -19210,8 +19210,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -19245,8 +19245,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -19280,8 +19280,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -19315,8 +19315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -19350,8 +19350,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -19385,8 +19385,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -19420,8 +19420,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -19455,8 +19455,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -19494,8 +19494,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -19529,8 +19529,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -19564,8 +19564,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -19599,8 +19599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -19634,8 +19634,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -19669,8 +19669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -19704,8 +19704,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -19739,8 +19739,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -19774,8 +19774,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -19809,8 +19809,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -19844,8 +19844,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -19879,8 +19879,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -19914,8 +19914,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -19949,8 +19949,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -19984,8 +19984,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -20021,8 +20021,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -20056,8 +20056,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -20091,8 +20091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -20128,8 +20128,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -20165,8 +20165,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -20208,8 +20208,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -20245,8 +20245,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -20280,8 +20280,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -20315,8 +20315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -20350,8 +20350,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -20385,8 +20385,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -20422,8 +20422,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -20457,8 +20457,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -20492,8 +20492,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -20527,8 +20527,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -20562,8 +20562,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -20599,8 +20599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -20640,8 +20640,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -20683,8 +20683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -20718,8 +20718,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -20757,8 +20757,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -20792,8 +20792,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -20833,8 +20833,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -20870,8 +20870,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -20907,8 +20907,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -20944,8 +20944,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -20983,8 +20983,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -21018,8 +21018,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -21055,8 +21055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -21090,8 +21090,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -21125,8 +21125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -21160,8 +21160,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -21195,8 +21195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -21230,8 +21230,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -21265,8 +21265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -21300,8 +21300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -21335,8 +21335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -21370,8 +21370,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -21405,8 +21405,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -21442,8 +21442,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -21477,8 +21477,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -21512,8 +21512,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -21547,8 +21547,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -21582,8 +21582,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -21617,8 +21617,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -21654,8 +21654,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -21689,8 +21689,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -21724,8 +21724,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -21759,8 +21759,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -21794,8 +21794,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -21829,8 +21829,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -21864,8 +21864,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -21899,8 +21899,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -21936,8 +21936,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -21979,8 +21979,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -22014,8 +22014,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -22049,8 +22049,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -22084,8 +22084,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -22125,8 +22125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -22162,8 +22162,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -22199,8 +22199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -22236,8 +22236,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -22275,8 +22275,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -22310,8 +22310,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -22345,8 +22345,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -22380,8 +22380,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -22415,8 +22415,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -22450,8 +22450,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -22485,8 +22485,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -22520,8 +22520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -22555,8 +22555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-1</v>
       </c>
@@ -22608,8 +22608,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-2</v>
       </c>
@@ -22651,8 +22651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-2-1</v>
       </c>
@@ -22696,8 +22696,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-2-2</v>
       </c>
